--- a/v1/剧本.xlsx
+++ b/v1/剧本.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\project\self_playing_ruler\v1\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819EB4E7-F86E-4EB9-B67A-7782E4E0355D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,23 +14,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="136" count="136">
   <si>
     <t>(无，纯音乐)</t>
   </si>
@@ -67,90 +50,648 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
       </rPr>
       <t>哆啦A梦？</t>
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
       </rPr>
       <t>）</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>乐曲BGM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>频道名/LOGO展示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>TODO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>加加鸽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>时长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>看到钢尺演奏很有意思</t>
+  </si>
+  <si>
+    <t>使用</t>
+  </si>
+  <si>
+    <t>xab</t>
+  </si>
+  <si>
+    <t>看到大神用钢尺演奏很有意思，于是就想模仿</t>
+  </si>
+  <si>
+    <t>但是没那个能力</t>
+  </si>
+  <si>
+    <t>所以只能用程序员的办法了</t>
+  </si>
+  <si>
+    <t>钢尺君/杯鸽等演奏片段</t>
+  </si>
+  <si>
+    <t>范大将军梗</t>
+  </si>
+  <si>
+    <t>但是“没那个能力”</t>
+  </si>
+  <si>
+    <t>程序猿图片</t>
+  </si>
+  <si>
+    <t>所以我决定做一个可以自动演奏的钢尺</t>
+  </si>
+  <si>
+    <t>哆啦A梦</t>
+  </si>
+  <si>
+    <t>过长动画</t>
+  </si>
+  <si>
+    <t>过长动画～</t>
+  </si>
+  <si>
+    <t>过场动画动画～</t>
+  </si>
+  <si>
+    <t>过场动画～</t>
+  </si>
+  <si>
+    <t>我的最初版设计手稿</t>
+  </si>
+  <si>
+    <t>但是太难了，我“没那个能力”</t>
+  </si>
+  <si>
+    <t>要实现钢尺演奏，需要一个夹持装置，将钢尺夹紧</t>
+  </si>
+  <si>
+    <t>要实现钢尺演奏，需要一个夹持装置将钢尺夹紧；一个直线运动机构改变钢尺的长短；一个拨动机构弹奏钢尺。于是我就先画一个草图</t>
+  </si>
+  <si>
+    <t>接下来就按照草图来建模</t>
+  </si>
+  <si>
+    <t>打印</t>
+  </si>
+  <si>
+    <t>组装模型与硬件</t>
+  </si>
+  <si>
+    <t>撸代码</t>
+  </si>
+  <si>
+    <t>建模</t>
+  </si>
+  <si>
+    <t>接下来就按照草图来初步设计，选择硬件</t>
+  </si>
+  <si>
+    <t>《你若三冬》</t>
+  </si>
+  <si>
+    <t>《你若三冬》DJ版</t>
+  </si>
+  <si>
+    <t>演奏并配上\0/组成的动效</t>
+  </si>
+  <si>
+    <t>验证版虽然已经可以演奏了，但速度与音准都不太理想，同时还需要使用串口发送音符比较不方便</t>
+  </si>
+  <si>
+    <t>演奏并配上\0/\o/\O/\0/组成的动效</t>
+  </si>
+  <si>
+    <t>掩饰曲目待定</t>
+  </si>
+  <si>
+    <t>演示曲目待定</t>
+  </si>
+  <si>
+    <t>验证版虽然已经可以演奏了，但速度与音准都不太理想，同时还需要使用串口发送音符比较不方便。硬件方面，使用开发板连线，集成度也太低了。</t>
+  </si>
+  <si>
+    <t>使用手机</t>
+  </si>
+  <si>
+    <t>所以接下来就要解决上述问题</t>
+  </si>
+  <si>
+    <t>验证版虽然已经可以演奏了，但速度与音准都不太理想，同时还需要使用串口发送音符比较不方便。硬件方面，使用开发板连线，集成度也太低了。所以接下来就要解决上述问题</t>
+  </si>
+  <si>
+    <t>验证版虽然已经可以演奏了，但存在挺多问题：速度与音准都不太理想，串口发送音符不方便。使用开发板连线，集成度低。</t>
+  </si>
+  <si>
+    <t>新版本外形轮廓</t>
+  </si>
+  <si>
+    <t>新版本外形轮廓（宝可梦——我是谁）</t>
+  </si>
+  <si>
+    <t>新版本就要解决这些问题</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证版虽然已经可以演奏了，但存在挺多问题：速度与音准都不太理想，串口发送音符不方便。使用开发板连线，集成度低。
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证版虽然已经可以演奏了，但存在挺多问题：速度与音准都不太理想，串口发送音符不方便。使用开发板连线，集成度低。
+</t>
+  </si>
+  <si>
+    <t>验证版虽然已经可以演奏了，但存在挺多问题：
+速度与音准都不太理想，串口发送音符不方便。使用开发板连线，集成度低。</t>
+  </si>
+  <si>
+    <t>验证版虽然已经可以演奏了，但存在挺多问题：
+速度与音准都不太理想、串口发送音符不方便、使用开发板连线集成度低、录音不方便</t>
+  </si>
+  <si>
+    <t>分屏
+左半屏
+右半屏：</t>
+  </si>
+  <si>
+    <r>
+      <t>成果展示，使用动态镜头视角（平移/缩放切换），演奏曲目（</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>哆啦A梦？</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>成果展示，使用动态镜头视角（平移/缩放切换），演奏曲目（</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="serif"/>
+      </rPr>
+      <t>哆啦A梦？</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="serif"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>成果展示，使用动态镜头视角（平移/缩放切换），演奏曲目（</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>哆啦A梦？</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color indexed="16777215"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>成果展示，使用动态镜头视角（平移/缩放切换），演奏曲目（</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color indexed="16777215"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>哆啦A梦？</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color indexed="16777215"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color indexed="16777215"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>成果展示，使用动态镜头视角（平移/缩放切换），演奏曲目（</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color indexed="16777215"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>哆啦A梦？</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color indexed="16777215"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>成果展示，使用动态镜头视角（平移/缩放切换），演奏曲目（</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>哆啦A梦？</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>成果展示，使用动态镜头视角（平移/缩放切换），演奏曲目（</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>哆啦A梦？</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>分屏
+左半屏：视频展示
+右半屏：问题依次浮现</t>
+  </si>
+  <si>
+    <t>左半屏：视频展示
+右半屏：问题依次浮现</t>
+  </si>
+  <si>
+    <t>首先，速度问题最重要，因为速度不够，很多个曲目无法演奏</t>
+  </si>
+  <si>
+    <t>钟》</t>
+  </si>
+  <si>
+    <t>《钟》</t>
+  </si>
+  <si>
+    <t>拆解一下当前演奏一个音符的流程：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拆解一下当前演奏一个音符的流程：
+</t>
+  </si>
+  <si>
+    <t>拆解一下当前演奏一个音符的流程：
+抬起舵机--&gt;移动钢尺--&gt;舵机按下--&gt;舵机拨动</t>
+  </si>
+  <si>
+    <t>其中</t>
+  </si>
+  <si>
+    <t>建模--&gt;打印--&gt;组装与连线--&gt; --&gt;</t>
+  </si>
+  <si>
+    <t>建模--&gt;打印--&gt;组装与连线--&gt;撸代码</t>
+  </si>
+  <si>
+    <t>相应的画面</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <vertAlign val="subscript"/>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t>cd</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="134"/>
+        <vertAlign val="superscript"/>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+      </rPr>
+      <t xml:space="preserve">    ab</t>
+    </r>
+  </si>
+  <si>
+    <t>其中舵机抬起与落下耗时最多，需要着重优化</t>
+  </si>
+  <si>
+    <t>此前录制的慢放</t>
+  </si>
+  <si>
+    <t>开头5秒黄金时间，必须炸裂。演示曲目待定</t>
+  </si>
+  <si>
+    <t>首先想到的就是加快按压钢尺的动作，更换更快速的舵机。</t>
+  </si>
+  <si>
+    <t>但仔细查找了一番之后发现，机械结构中：速度快、力量大、体积小是一个不可能三角，最多只能取其二</t>
+  </si>
+  <si>
+    <t>这个三角的动效</t>
+  </si>
+  <si>
+    <t>想到钢尺是铁的，可以使用电磁铁把它吸住</t>
+  </si>
+  <si>
+    <t>这个三角的动效
+舵机：力量大、体积小、速度慢
+无刷电机：速度快、体积小，力量小</t>
+  </si>
+  <si>
+    <t>但仔细查找了一番之后发现，机械结构中：速度快、力量大、体积小是一个不可能三角，最多只能取其二
+sg90舵机：力量大、体积小、速度慢
+foc无刷电机：速度快、体积小，力量小
+42步进电机：速度快、力量大、体积大</t>
+  </si>
+  <si>
+    <t>三角动效，配上不同的器件</t>
+  </si>
+  <si>
+    <t>此前录制的慢放视频</t>
+  </si>
+  <si>
+    <t>买回来测试，效果很好</t>
+  </si>
+  <si>
+    <t>其次，使用</t>
+  </si>
+  <si>
+    <t>其次，丝杆步进电机</t>
+  </si>
+  <si>
+    <t>但仔细查找了一番之后发现，机械结构中：速度快、力量大、体积小是一个不可能三角，最多只能取其二
+sg90舵机：力量大、体积小、速度慢
+foc无刷电机：速度快、体积小，力量小
+3D打印机常用的42步进电机：速度快、力量大、体积大</t>
+  </si>
+  <si>
+    <t>其次，丝杆步进电机，</t>
+  </si>
+  <si>
+    <t>其次，丝杆步进电机，的移动速度也加快。参考光驱中的设计，需要增加导轨，减小阻力</t>
+  </si>
+  <si>
+    <t>华强买瓜</t>
+  </si>
+  <si>
+    <t>”</t>
+  </si>
+  <si>
+    <t>“华强买瓜”</t>
+  </si>
+  <si>
+    <t>那，吸铁石（华强买瓜语音）</t>
+  </si>
+  <si>
+    <t>画中画）</t>
+  </si>
+  <si>
+    <t>电磁铁吸住钢尺
+画中画华强：买瓜</t>
+  </si>
+  <si>
+    <t>电磁铁吸住钢尺
+画中画：华强买瓜</t>
+  </si>
+  <si>
+    <t>光驱内部结构</t>
+  </si>
+  <si>
+    <t>两外，丝杆步进电机，的移动速度也加快。参考光驱中的设计，需要增加导轨，减小阻力</t>
+  </si>
+  <si>
+    <t>其次，就要优化音准。此前是在桌面测试了几个长度的音高，换算出频率-长度函数。但这样并不准确</t>
+  </si>
+  <si>
+    <t>其次，就要优化音准。此前是在桌面测试了几个长度的音高，换算出频率-长度函数。但这样人工测量非常耗时，而且并不准确</t>
+  </si>
+  <si>
+    <t>拨动钢尺，用手机测量频率</t>
+  </si>
+  <si>
+    <t>实现自动调音，加入麦克风</t>
+  </si>
+  <si>
+    <t>验证版虽然已经可以演奏了，但存在挺多问题：
+速度与音准都不太理想、串口发送音符不方便、使用开发板连线集成度低</t>
+  </si>
+  <si>
+    <t>添加一个麦克风，使用程序控制拨动钢尺的不同长度，对麦克风采集到的音频进行傅里叶变换，得到相应的频率</t>
+  </si>
+  <si>
+    <t>添加一个麦克风，使用程序控制拨动钢尺的不同长度，对麦克风采集到的音频进行傅里叶变换，得到频率。最终拟合出一个高精度的频率-步数(step)函数</t>
+  </si>
+  <si>
+    <t>使用串口发送音符，很不方便。</t>
+  </si>
+  <si>
+    <t>主流的电子乐器与宿主软件都支持midi输入输出。并且所以决定使用usb midi</t>
+  </si>
+  <si>
+    <t>主流的电子乐器与宿主软件都支持midi输入输出。并且esp32s3开发板刚好有usb接口，所以决定使用usb midi作为音乐接口</t>
+  </si>
+  <si>
+    <t>MIDI简介</t>
+  </si>
+  <si>
+    <t>----------------</t>
+  </si>
+  <si>
+    <t>使用串口发送音符，很不方便，也不能兼容主流乐谱。</t>
+  </si>
+  <si>
+    <t>使用串口发送音符，很不方便，还需要自己手写乐谱。</t>
+  </si>
+  <si>
+    <t>MIDI简介（待补充）</t>
+  </si>
+  <si>
+    <t>按照新的设计</t>
+  </si>
+  <si>
+    <t>其中舵机抬起与落下耗时最多，需要着重优化。首先想到的就是加快按压钢尺的动作，更换更快速的舵机。</t>
+  </si>
+  <si>
+    <t>麦克风--》</t>
+  </si>
+  <si>
+    <t>麦克风--&gt;正弦信号--&gt;频率图</t>
+  </si>
+  <si>
+    <t>按照新的设计：建模--&gt;打印--&gt;组装与连线--&gt;撸代码--&gt;--&gt;</t>
+  </si>
+  <si>
+    <t>按照新的设计：建模--&gt;打印--&gt;组装与连线--&gt;撸代码</t>
+  </si>
+  <si>
+    <t>相应的画面（快放）</t>
+  </si>
+  <si>
+    <t>测试OK</t>
+  </si>
+  <si>
+    <t>测试画面（）</t>
+  </si>
+  <si>
+    <t>测试画面</t>
+  </si>
+  <si>
+    <t>测试（待补充）</t>
+  </si>
+  <si>
+    <t>验证方案可行后，就要把这坨东西整合起来了</t>
+  </si>
+  <si>
+    <t>杂乱的开发板连线</t>
+  </si>
+  <si>
+    <t>首先需要画一个电路板，把开发板与各种元器件连接起来</t>
+  </si>
+  <si>
+    <t>连线图</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="45" formatCode="mm:ss"/>
+    <numFmt numFmtId="21" formatCode="h:mm:ss"/>
+  </numFmts>
+  <fonts count="4">
     <font>
+      <name val="等线"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
       <b/>
+      <charset val="134"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -162,12 +703,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -190,44 +731,98 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="45" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="21" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="45" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16" count="0"/>
 </styleSheet>
 </file>
 
@@ -484,30 +1079,25 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="28.05" customHeight="1" x14ac:dyDescent="0.5"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:O32"/>
+  <sheetFormatPr defaultRowHeight="28.05" customHeight="1" defaultColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="4.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="85.265625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="75.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" customWidth="1" bestFit="1" width="4.9296875" style="1"/>
+    <col min="2" max="2" customWidth="1" bestFit="1" width="6.1992188" style="1"/>
+    <col min="3" max="3" customWidth="1" bestFit="1" width="13.1328125" style="1"/>
+    <col min="4" max="4" customWidth="1" width="68.71094" style="1"/>
+    <col min="5" max="5" customWidth="1" bestFit="1" width="75.66406" style="1"/>
+    <col min="6" max="6" customWidth="1" bestFit="1" width="29.199219" style="1"/>
+    <col min="7" max="7" customWidth="1" bestFit="1" width="38.796875" style="1"/>
+    <col min="8" max="16384" customWidth="0" width="9.066406" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="8:8" ht="28.05" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -530,163 +1120,322 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6">
+    <row r="2" spans="8:8" ht="28.05" customHeight="1">
+      <c r="A2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="G2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="8:8" ht="28.05" customHeight="1">
+      <c r="A3" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <f>C2+B2</f>
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="D3" s="2" t="s">
+        <v>1.15740740740741E-4</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4">
+    <row r="4" spans="8:8" ht="28.05" customHeight="1">
+      <c r="A4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C4" s="5">
         <f>C3+B3</f>
-        <v>1.7361111111111109E-4</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
+        <v>1.7361111111111142E-4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="8:8" ht="28.05" customHeight="1">
+      <c r="A5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C5" s="5">
         <f>C4+B4</f>
-        <v>1.7361111111111109E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4">
-        <f t="shared" ref="C4:C14" si="0">C5+B5</f>
-        <v>1.7361111111111109E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4">
-        <f t="shared" si="0"/>
-        <v>1.7361111111111109E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4">
-        <f t="shared" si="0"/>
-        <v>1.7361111111111109E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="6">
-        <v>0</v>
-      </c>
-      <c r="C9" s="4">
-        <f t="shared" si="0"/>
-        <v>1.7361111111111109E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="6">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4">
-        <f t="shared" si="0"/>
-        <v>1.7361111111111109E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="6">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4">
-        <f t="shared" si="0"/>
-        <v>1.7361111111111109E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="6">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4">
-        <f t="shared" si="0"/>
-        <v>1.7361111111111109E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B13" s="6">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4">
-        <f t="shared" si="0"/>
-        <v>1.7361111111111109E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="6">
-        <v>0</v>
-      </c>
-      <c r="C14" s="4">
-        <f t="shared" si="0"/>
-        <v>1.7361111111111109E-4</v>
+        <v>1.73611111111111E-4</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8" ht="28.05" customHeight="1">
+      <c r="A6" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="5">
+        <f>C5+B5</f>
+        <v>1.73611111111111E-4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8" ht="28.05" customHeight="1">
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8" ht="28.05" customHeight="1">
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8" ht="28.05" customHeight="1">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9"/>
+      <c r="E9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="8:8" ht="28.05" customHeight="1">
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="8:8" ht="28.05" customHeight="1">
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11"/>
+      <c r="F11" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="8:8" ht="28.05" customHeight="1">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="8:8" ht="28.05" customHeight="1">
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13"/>
+      <c r="E13" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="8:8" ht="28.05" customHeight="1">
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="8:8" ht="28.05">
+      <c r="D15" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="8:8" ht="28.05" customHeight="1">
+      <c r="D16" s="13"/>
+      <c r="E16" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+    </row>
+    <row r="17" spans="8:8" ht="54.15">
+      <c r="D17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" ht="28.05">
+      <c r="D18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="D19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8" ht="28.05">
+      <c r="D20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="8:8" ht="28.05" customHeight="1">
+      <c r="D21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="8:8">
+      <c r="D22" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="8:8">
+      <c r="D23" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="8:8">
+      <c r="E24" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="8:8">
+      <c r="D25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="8:8">
+      <c r="E26" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="8:8">
+      <c r="D27" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="8:8">
+      <c r="D28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="8:8">
+      <c r="D29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="8:8">
+      <c r="D30" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="8:8">
+      <c r="D31" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="8:8">
+      <c r="D32" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/v1/剧本.xlsx
+++ b/v1/剧本.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="136" count="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="207" count="207">
   <si>
     <t>(无，纯音乐)</t>
   </si>
@@ -658,6 +658,220 @@
   </si>
   <si>
     <t>连线图</t>
+  </si>
+  <si>
+    <t>既然为了调音增加了麦克风硬件，那为什么不物尽其用呢？</t>
+  </si>
+  <si>
+    <t>主流的电子乐器与宿主软件都支持midi输入输出。所以决定使用usb midi作为音乐接口</t>
+  </si>
+  <si>
+    <t>既然为了调音增加了麦克风硬件，那为什么不物尽其用呢？esp32s3开发板刚好有usb接口，可以集成一个usb麦克风，用来录音。</t>
+  </si>
+  <si>
+    <t>首先需一个电路板，把开发板与各种元器件连接起来</t>
+  </si>
+  <si>
+    <t>pcb</t>
+  </si>
+  <si>
+    <t>原理图/pcb</t>
+  </si>
+  <si>
+    <t>pcb展示</t>
+  </si>
+  <si>
+    <t>响指</t>
+  </si>
+  <si>
+    <t>在屏幕前打一个响指，从屏幕中取出PCB</t>
+  </si>
+  <si>
+    <t>焊接各种功能元件</t>
+  </si>
+  <si>
+    <t>几个焊接特写</t>
+  </si>
+  <si>
+    <t>BGM待添加</t>
+  </si>
+  <si>
+    <t>重新建模，将主板与钢尺、电机等整合在一起</t>
+  </si>
+  <si>
+    <t>模型爆炸图</t>
+  </si>
+  <si>
+    <t>3d打印延迟摄影</t>
+  </si>
+  <si>
+    <t>取出模型</t>
+  </si>
+  <si>
+    <t>一些组装的特写，待补充</t>
+  </si>
+  <si>
+    <t>组装过程特写：</t>
+  </si>
+  <si>
+    <t>组装过程特写：
+以安装卡扣，拧螺丝为主</t>
+  </si>
+  <si>
+    <t>成品展示：使用旋转展示台</t>
+  </si>
+  <si>
+    <t>哆啦A梦掏出物品：自动演奏的钢尺</t>
+  </si>
+  <si>
+    <t>首先要想一个基本的设计方案</t>
+  </si>
+  <si>
+    <t>这里我使用</t>
+  </si>
+  <si>
+    <t>这里我使用光驱的丝杆步进电机</t>
+  </si>
+  <si>
+    <t>首先要设计一个原型机，验证一下方案可行性。基本思路是：体积小巧，价格便宜，方便复刻</t>
+  </si>
+  <si>
+    <t>首先要设计一个原型机，验证一下方案可行性。基本思路是：体积小巧，价格便宜</t>
+  </si>
+  <si>
+    <t>为了更方便复刻，就只使用</t>
+  </si>
+  <si>
+    <t>为了更方便复刻，就只使用成品模块，不做单独的pcb了</t>
+  </si>
+  <si>
+    <t>首先需一个电路板，各种元器件连接起来</t>
+  </si>
+  <si>
+    <t>接下来就到了我的舒适区，撸代码</t>
+  </si>
+  <si>
+    <t>使用光驱的丝杆步进电机来控制钢尺移动，使用2个舵机分别压住钢尺与弹拨钢尺</t>
+  </si>
+  <si>
+    <t>设计图展示+器件特写</t>
+  </si>
+  <si>
+    <t>接下来就到了程序猿的舒适区，撸代码</t>
+  </si>
+  <si>
+    <t>电磁铁的驱动、fft</t>
+  </si>
+  <si>
+    <t>主要模块的代码展示</t>
+  </si>
+  <si>
+    <t>编译、烧写、启动</t>
+  </si>
+  <si>
+    <t>接下来就到了程序猿的舒适区，撸代码！！！</t>
+  </si>
+  <si>
+    <t>在写了亿点点代码，解决了亿点点bug之后，终于</t>
+  </si>
+  <si>
+    <t>王国之泪BGM</t>
+  </si>
+  <si>
+    <t>插入电源、数据线、连接宿主软件、播放音乐（塞尔达主题曲）</t>
+  </si>
+  <si>
+    <t>插入电源、数据线、连接宿主软件、</t>
+  </si>
+  <si>
+    <t>开始弹奏后，bgm关掉</t>
+  </si>
+  <si>
+    <t>nice</t>
+  </si>
+  <si>
+    <t>nice老哥</t>
+  </si>
+  <si>
+    <t>你甚至于可以用它来当做一个麦克风用</t>
+  </si>
+  <si>
+    <t>手持钢尺琴唱歌</t>
+  </si>
+  <si>
+    <t>歌曲待定</t>
+  </si>
+  <si>
+    <t>一只钢尺演奏难免有些单调，于是我有做了两个，组成3个声部。下面就来演奏一个卡农</t>
+  </si>
+  <si>
+    <t>一只钢尺演奏难免有些单调，于是我又做了两个，组成3个声部。下面就来演奏一个卡农</t>
+  </si>
+  <si>
+    <t>一只钢尺演奏难免有些单调，于是我又做了两个，组成成和声</t>
+  </si>
+  <si>
+    <t>演奏卡农</t>
+  </si>
+  <si>
+    <t>由于钢尺本身还有一个</t>
+  </si>
+  <si>
+    <t>一只钢尺演奏难免有些单调，于是我又做了两个，组成成和声。最后以卡农来结尾吧。</t>
+  </si>
+  <si>
+    <t>由于有mic，还可以对音色进行一些处理</t>
+  </si>
+  <si>
+    <t>插入电源、数据线、连接宿主软件、使用MIDI键盘弹奏塞尔达主题曲</t>
+  </si>
+  <si>
+    <t>由于有mic，还可以对声音进行一些处理，比如对强弱的支持，添加一些效果器等等</t>
+  </si>
+  <si>
+    <t>midi键盘演示强弱、歌曲演示效果器</t>
+  </si>
+  <si>
+    <t>一只钢尺演奏难免有些单调，</t>
+  </si>
+  <si>
+    <t>于是我又做了两个，组成成和声。最后以卡农来结尾吧。</t>
+  </si>
+  <si>
+    <t>一只钢尺演奏难免有些单调，所以我希望组一个文具乐队。</t>
+  </si>
+  <si>
+    <t>动次打次</t>
+  </si>
+  <si>
+    <t>pen beats演示</t>
+  </si>
+  <si>
+    <t>演示</t>
+  </si>
+  <si>
+    <t>笔吹奏演示</t>
+  </si>
+  <si>
+    <t>打击声部pen beats演示</t>
+  </si>
+  <si>
+    <t>打击乐：动次打次</t>
+  </si>
+  <si>
+    <t>管乐</t>
+  </si>
+  <si>
+    <t>不过上面这些还没有实现，如果这类视频观众朋友门喜欢，我后续会做。</t>
+  </si>
+  <si>
+    <t>又做了两个，组成成和声。最后以卡农来结尾吧。</t>
+  </si>
+  <si>
+    <t>增加两个，组成三声部，以卡农为结尾</t>
+  </si>
+  <si>
+    <t>无</t>
   </si>
 </sst>
 </file>
@@ -669,7 +883,7 @@
     <numFmt numFmtId="45" formatCode="mm:ss"/>
     <numFmt numFmtId="21" formatCode="h:mm:ss"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="等线"/>
       <sz val="11"/>
@@ -693,6 +907,16 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -708,7 +932,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -748,6 +972,19 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -768,13 +1005,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -796,26 +1046,44 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="45" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1084,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultRowHeight="28.05" customHeight="1" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" bestFit="1" width="4.9296875" style="1"/>
@@ -1222,218 +1490,399 @@
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="8:8" ht="28.05" customHeight="1">
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="7" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="8:8" ht="28.05" customHeight="1">
+    <row r="9" spans="8:8" ht="28.05" customFormat="1">
+      <c r="A9" s="10"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
-      <c r="D9"/>
-      <c r="E9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="8:8" ht="28.05" customHeight="1">
+      <c r="D9" s="11"/>
+      <c r="E9" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="8:8" ht="28.05" customFormat="1">
+      <c r="A10" s="10"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="D10" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="8:8" ht="28.05" customHeight="1">
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
       <c r="D11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11"/>
-      <c r="F11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>46</v>
+        <v>127</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="8:8" ht="28.05" customHeight="1">
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
       <c r="D12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+        <v>44</v>
+      </c>
+      <c r="E12"/>
+      <c r="F12" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="13" spans="8:8" ht="28.05" customHeight="1">
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
-      <c r="D13"/>
-      <c r="E13" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
+      <c r="D13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="8:8" ht="28.05" customHeight="1">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="8" t="s">
+      <c r="D14"/>
+      <c r="E14" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+    </row>
+    <row r="15" spans="8:8" ht="28.05" customHeight="1">
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E15" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="9" t="s">
+      <c r="F15" s="15"/>
+      <c r="G15" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="8:8" ht="28.05">
-      <c r="D15" s="11" t="s">
+    <row r="16" spans="8:8" ht="28.05">
+      <c r="D16" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E16" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-    </row>
-    <row r="16" spans="8:8" ht="28.05" customHeight="1">
-      <c r="D16" s="13"/>
-      <c r="E16" s="10" t="s">
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" spans="8:8" ht="28.05" customHeight="1">
+      <c r="D17" s="17"/>
+      <c r="E17" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-    </row>
-    <row r="17" spans="8:8" ht="54.15">
-      <c r="D17" s="1" t="s">
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+    </row>
+    <row r="18" spans="8:8" ht="54.15">
+      <c r="D18" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="8:8" ht="28.05">
-      <c r="D18" s="1" t="s">
+    <row r="19" spans="8:8" ht="28.05">
+      <c r="D19" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="8:8">
-      <c r="D19" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="20" spans="8:8" ht="28.05">
       <c r="D20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="8:8" ht="28.05">
+      <c r="D21" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="8:8" ht="28.05" customHeight="1">
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="8:8" ht="28.05" customHeight="1">
+      <c r="D22" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="8:8">
-      <c r="D22" s="1" t="s">
+    <row r="23" spans="8:8" ht="28.05">
+      <c r="D23" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E23" s="18" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="8:8">
-      <c r="D23" s="1" t="s">
+    <row r="24" spans="8:8" ht="28.05" customFormat="1">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="19" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="24" spans="8:8">
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="1"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" spans="8:8" ht="28.05" customFormat="1">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" spans="8:8" ht="28.05">
+      <c r="D26" s="19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="8:8" ht="28.05">
+      <c r="E27" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="8:8">
-      <c r="D25" s="1" t="s">
+    <row r="28" spans="8:8" ht="28.05">
+      <c r="D28" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E28" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="8:8">
-      <c r="E26" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="8:8">
-      <c r="D27" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" spans="8:8">
-      <c r="D28" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="8:8">
-      <c r="D29" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="30" spans="8:8">
+    <row r="29" spans="8:8" ht="28.05">
+      <c r="E29" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="8:8" ht="28.05">
       <c r="D30" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="8:8">
+    <row r="31" spans="8:8" ht="28.05">
       <c r="D31" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="8:8" ht="28.05">
+      <c r="D32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="8:8" ht="28.05">
+      <c r="D33" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="8:8" ht="28.05">
+      <c r="D34" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="8:8">
-      <c r="D32" s="1" t="s">
+    <row r="35" spans="8:8" ht="28.05">
+      <c r="D35" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>134</v>
-      </c>
+      <c r="E35" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="8:8" ht="28.05">
+      <c r="D36" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="8:8" ht="28.05">
+      <c r="D37" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="8:8" ht="28.05">
+      <c r="D38" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="39" spans="8:8" ht="28.05">
+      <c r="D39" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="8:8">
+      <c r="D40" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="41" spans="8:8">
+      <c r="D41" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="42" spans="8:8">
+      <c r="D42" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="8:8">
+      <c r="D43" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="8:8">
+      <c r="D44" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="8:8">
+      <c r="D45" s="1"/>
+      <c r="E45" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="8:8">
+      <c r="D46" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="47" spans="8:8">
+      <c r="D47" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="48" spans="8:8">
+      <c r="D48" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="49" spans="8:8">
+      <c r="E49" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="8:8">
+      <c r="D50" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="8:8">
+      <c r="D51" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="52" spans="8:8">
+      <c r="E52" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="53" spans="8:8">
+      <c r="E53" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" spans="8:8">
+      <c r="D54" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F54" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
